--- a/upload/pagamentorp2026.xlsx
+++ b/upload/pagamentorp2026.xlsx
@@ -2943,7 +2943,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1459840.09</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
